--- a/Д-4.xlsx
+++ b/Д-4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Expert-E5D\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0909668-A5FF-496B-B5D7-7BEF7B1E646E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A133BA-1C5E-47A8-88CE-A8EE401ED4BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1464" yWindow="1464" windowWidth="33348" windowHeight="14964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="1596" windowWidth="33348" windowHeight="14964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Вопросы" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="470">
   <si>
     <t>id</t>
   </si>
@@ -1412,6 +1412,25 @@
   </si>
   <si>
     <t>Скорость в к-ой области</t>
+  </si>
+  <si>
+    <t>Какая стадия в общей схеме развития аварии и в типовых сценариях аварийного выброса широкой фракции легких углеводородов (ШФЛУ) на месте разгерметизации линейной части трубопровода при анализе последствий аварийного выброса является верной согласно Руководству по безопасности «Методические рекомендации по проведению количественного анализа риска аварий на конденсатопроводах и продуктопроводах», утвержденному приказом Ростехнадзора от 17.02.2023 № 69?</t>
+  </si>
+  <si>
+    <t>Начало истечения ШФЛУ из трубопровода в напорном режиме в окружающую среду, в т.ч. в воду при прохождении трубопровода по дну водоемов</t>
+  </si>
+  <si>
+    <t>Начало истечения ШФЛУ из трубопровода в безнапорном режиме в окружающую среду, в т.ч. в воду при прохождении трубопровода по дну водоемов</t>
+  </si>
+  <si>
+    <t>Вскипание ШФЛУ в трубопроводе и образование однофазного потока в трубопроводе</t>
+  </si>
+  <si>
+    <t>Образование на месте выброса ШФЛУ из трубопровода облака газа (и при определенных обстоятельствах капель), нагретых до температуры кипения; неинтенсивное смешение ШФЛУ с воздухом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+Все ответы не верны</t>
   </si>
 </sst>
 </file>
@@ -1457,7 +1476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1467,6 +1486,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1770,7 +1792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -4579,6 +4601,32 @@
         <v>2</v>
       </c>
     </row>
+    <row r="103" spans="1:9" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A103" s="3">
+        <v>102</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
